--- a/dataset/construct/dataset_splits/data_size/50_percent/tum/fold1.xlsx
+++ b/dataset/construct/dataset_splits/data_size/50_percent/tum/fold1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN27"/>
+  <dimension ref="A1:AK27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>603</v>
+        <v>464</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,79 +625,79 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>77.0139021978858</v>
+        <v>88.22278655537809</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>31.25</v>
       </c>
       <c r="E2" t="n">
-        <v>37.2536452491587</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>60</v>
+        <v>490</v>
       </c>
       <c r="I2" t="n">
-        <v>909</v>
+        <v>661</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>651</v>
       </c>
       <c r="K2" t="n">
-        <v>656</v>
+        <v>1802</v>
       </c>
       <c r="L2" t="n">
-        <v>552</v>
+        <v>129</v>
       </c>
       <c r="M2" t="n">
-        <v>193</v>
+        <v>228</v>
       </c>
       <c r="N2" t="n">
-        <v>1401</v>
+        <v>183</v>
       </c>
       <c r="O2" t="n">
-        <v>96</v>
+        <v>540</v>
       </c>
       <c r="P2" t="n">
-        <v>84</v>
+        <v>7</v>
       </c>
       <c r="Q2" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="R2" t="n">
-        <v>193</v>
+        <v>135</v>
       </c>
       <c r="S2" t="n">
-        <v>46</v>
+        <v>163</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>20.65</v>
       </c>
       <c r="V2" t="n">
-        <v>46</v>
+        <v>0.16</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>20.690094219506</v>
       </c>
       <c r="X2" t="n">
-        <v>24.9</v>
+        <v>20.4636637734958</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.148698884758364</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
-        <v>26.1013496307614</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>25.0246489572143</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -730,33 +715,24 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="AK2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>86</v>
-      </c>
-      <c r="AN2" t="n">
         <v>170</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>610</v>
+        <v>361</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -764,79 +740,79 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>80.4444026161685</v>
+        <v>78.027219623799</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>26.6097125450789</v>
       </c>
       <c r="E3" t="n">
-        <v>38.7396694214876</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>45</v>
+        <v>276</v>
       </c>
       <c r="I3" t="n">
-        <v>3400</v>
+        <v>295</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>161</v>
       </c>
       <c r="K3" t="n">
-        <v>966</v>
+        <v>732</v>
       </c>
       <c r="L3" t="n">
-        <v>1037</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2224</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>24.05</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>24.5098039215686</v>
       </c>
       <c r="X3" t="n">
-        <v>29.95</v>
+        <v>23.7993692983298</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.263768115942029</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="n">
-        <v>31.5126050420168</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>30.3986119121575</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -863,22 +839,15 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AK3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
+        <v>156</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>294</v>
+        <v>702</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -886,86 +855,88 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>85.3537317793495</v>
+        <v>79.79584759297281</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>22.3863142771225</v>
       </c>
       <c r="E4" t="n">
-        <v>22.9590876585494</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>60</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>692</v>
+      </c>
+      <c r="I4" t="n">
+        <v>591</v>
+      </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>166</v>
       </c>
       <c r="K4" t="n">
-        <v>628</v>
+        <v>1449</v>
       </c>
       <c r="L4" t="n">
-        <v>245</v>
+        <v>82</v>
       </c>
       <c r="M4" t="n">
-        <v>383</v>
+        <v>51</v>
       </c>
       <c r="N4" t="n">
-        <v>1256</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>6.3</v>
+        <v>133</v>
       </c>
       <c r="P4" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="Q4" t="n">
-        <v>157</v>
+        <v>11</v>
       </c>
       <c r="R4" t="n">
-        <v>184.3</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>94</v>
+        <v>24.6</v>
       </c>
       <c r="V4" t="n">
-        <v>94</v>
+        <v>0.27</v>
       </c>
       <c r="W4" t="n">
-        <v>2</v>
+        <v>25.4647313470843</v>
       </c>
       <c r="X4" t="n">
-        <v>25.15</v>
+        <v>24.8459903311873</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.235087719298246</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>25.9103641456583</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>25.3028496612552</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
@@ -974,31 +945,24 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN4" t="inlineStr"/>
+        <v>116</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>348</v>
+        <v>604</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1006,86 +970,88 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>88.94842941161561</v>
+        <v>89.1044661190965</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>23.046875</v>
       </c>
       <c r="E5" t="n">
-        <v>22.5878330942278</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>42</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>1163</v>
+      </c>
+      <c r="I5" t="n">
+        <v>612</v>
+      </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>798</v>
       </c>
       <c r="K5" t="n">
-        <v>114</v>
+        <v>2573</v>
       </c>
       <c r="L5" t="n">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="M5" t="n">
-        <v>336</v>
+        <v>24</v>
       </c>
       <c r="N5" t="n">
-        <v>557</v>
+        <v>30</v>
       </c>
       <c r="O5" t="n">
-        <v>26</v>
+        <v>140</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q5" t="n">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>286</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>174</v>
+        <v>25.75</v>
       </c>
       <c r="V5" t="n">
-        <v>180</v>
+        <v>0.15</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>25.8785332314744</v>
       </c>
       <c r="X5" t="n">
-        <v>23.65</v>
+        <v>25.4533139190353</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.286231884057971</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>23.554876496053</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>23.0660688205498</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1094,31 +1060,24 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>98</v>
-      </c>
-      <c r="AN5" t="inlineStr"/>
+        <v>230</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>597</v>
+        <v>634</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1126,79 +1085,79 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>80.8852175070348</v>
+        <v>85.36462278500269</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>30.4271978579252</v>
       </c>
       <c r="E6" t="n">
-        <v>24.9680097375237</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="I6" t="n">
-        <v>1360</v>
+        <v>26.4</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>532</v>
+        <v>104.4</v>
       </c>
       <c r="L6" t="n">
-        <v>615</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>593</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1740</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>22.9</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>23.2365673542144</v>
       </c>
       <c r="X6" t="n">
-        <v>28.1</v>
+        <v>22.6736985933985</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.187096774193548</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>28.6478227654698</v>
+        <v>1</v>
       </c>
       <c r="AA6" t="n">
-        <v>27.9784080907002</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1219,28 +1178,21 @@
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="AK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN6" t="inlineStr"/>
+        <v>186</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>528</v>
+        <v>326</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1248,85 +1200,85 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>84.2009601490608</v>
+        <v>83.6231034362562</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>24.0238086700849</v>
       </c>
       <c r="E7" t="n">
-        <v>20.5498866213151</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>60</v>
+        <v>196.4</v>
       </c>
       <c r="I7" t="n">
-        <v>786</v>
+        <v>35.3</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>124.8</v>
       </c>
       <c r="K7" t="n">
-        <v>118.2</v>
+        <v>356.5</v>
       </c>
       <c r="L7" t="n">
-        <v>74.2</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>82.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>275</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>35.2</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>41.7</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>14.2</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>13.8</v>
+        <v>22.9</v>
       </c>
       <c r="V7" t="n">
-        <v>28</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>23.2365673542144</v>
       </c>
       <c r="X7" t="n">
-        <v>22.9</v>
+        <v>22.6484228950307</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.297397769516729</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="n">
-        <v>22.8545963840081</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>22.0850401322991</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1335,7 +1287,7 @@
         <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1347,24 +1299,13 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>74</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>156</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="AK7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>972</v>
+        <v>2001</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1372,85 +1313,85 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>75.86468343600269</v>
+        <v>78.18058825766219</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>30.078125</v>
       </c>
       <c r="E8" t="n">
-        <v>27.6816608996539</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>47</v>
+        <v>180.1</v>
       </c>
       <c r="I8" t="n">
-        <v>3860</v>
+        <v>222.6</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>117.4</v>
       </c>
       <c r="K8" t="n">
-        <v>1186</v>
+        <v>520.1</v>
       </c>
       <c r="L8" t="n">
-        <v>1048</v>
+        <v>12.6</v>
       </c>
       <c r="M8" t="n">
-        <v>1330</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3564</v>
+        <v>16.8</v>
       </c>
       <c r="O8" t="n">
-        <v>270</v>
+        <v>29.4</v>
       </c>
       <c r="P8" t="n">
-        <v>228</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>738</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>108</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>124</v>
+        <v>24.15</v>
       </c>
       <c r="V8" t="n">
-        <v>394</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>24.0005092946269</v>
       </c>
       <c r="X8" t="n">
-        <v>29.9</v>
+        <v>23.7029066974866</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.204204204204204</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>29.921059332824</v>
+        <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>29.3765161028151</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1459,34 +1400,27 @@
         <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AK8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>114</v>
-      </c>
-      <c r="AN8" t="inlineStr"/>
+        <v>152</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1870</v>
+        <v>1997</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1494,85 +1428,85 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>75.305613449692</v>
+        <v>80.8359181940325</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>23.309053069719</v>
       </c>
       <c r="E9" t="n">
-        <v>28.3059950645957</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>60</v>
+        <v>91.8</v>
       </c>
       <c r="I9" t="n">
-        <v>482</v>
+        <v>81.7</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>52.5</v>
       </c>
       <c r="K9" t="n">
-        <v>203.8</v>
+        <v>226</v>
       </c>
       <c r="L9" t="n">
-        <v>177.1</v>
+        <v>18.2</v>
       </c>
       <c r="M9" t="n">
-        <v>101.3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>482.2</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>14.5</v>
+        <v>18.2</v>
       </c>
       <c r="P9" t="n">
-        <v>13.4</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>40.9</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>10.3</v>
+        <v>21.4</v>
       </c>
       <c r="V9" t="n">
-        <v>10.3</v>
+        <v>0.22</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>22.0588235294118</v>
       </c>
       <c r="X9" t="n">
-        <v>22.45</v>
+        <v>21.710123730909</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.23921568627451</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>22.7591036414566</v>
+        <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>21.6661077559205</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1590,27 +1524,18 @@
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>78</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>166</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1962</v>
+        <v>2013</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1618,79 +1543,79 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>74.1123504322255</v>
+        <v>92.0309740284432</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>26.7949380165289</v>
       </c>
       <c r="E10" t="n">
-        <v>25.0593070266296</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>30</v>
+        <v>262.3</v>
       </c>
       <c r="I10" t="n">
-        <v>35000</v>
+        <v>377.1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>280.3</v>
       </c>
       <c r="K10" t="n">
-        <v>783.1</v>
+        <v>919.7</v>
       </c>
       <c r="L10" t="n">
-        <v>744.9</v>
+        <v>7.6</v>
       </c>
       <c r="M10" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1697</v>
+        <v>29.1</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4</v>
+        <v>36.7</v>
       </c>
       <c r="P10" t="n">
-        <v>196.2</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>196.6</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>92.3</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>24.6</v>
       </c>
       <c r="V10" t="n">
-        <v>92.3</v>
+        <v>0.12</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>24.5098039215686</v>
       </c>
       <c r="X10" t="n">
-        <v>28.15</v>
+        <v>26.4561900936673</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.19551282051282</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>28.5841609371021</v>
+        <v>1</v>
       </c>
       <c r="AA10" t="n">
-        <v>28.1846427181971</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1711,30 +1636,19 @@
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>142</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>156</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="AK10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>361</v>
+        <v>1705</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1742,80 +1656,82 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>78.027219623799</v>
+        <v>85.11794274596291</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>23.0400201994697</v>
       </c>
       <c r="E11" t="n">
-        <v>26.6097125450789</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>60</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
+        <v>1413.6</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1288</v>
+      </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>1236</v>
       </c>
       <c r="K11" t="n">
-        <v>276</v>
+        <v>3937.6</v>
       </c>
       <c r="L11" t="n">
-        <v>295</v>
+        <v>379</v>
       </c>
       <c r="M11" t="n">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="N11" t="n">
-        <v>732</v>
+        <v>492</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>997</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>851.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>30.15</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>29.8892284186402</v>
       </c>
       <c r="X11" t="n">
-        <v>24.05</v>
+        <v>29.6417868004739</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.282142857142857</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>24.5098039215686</v>
+        <v>1</v>
       </c>
       <c r="AA11" t="n">
-        <v>23.7993692983298</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1824,39 +1740,30 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="AK11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>84</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>156</v>
+        <v>232</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>562</v>
+        <v>1356</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1864,123 +1771,112 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>85.7368640200776</v>
+        <v>78.99659071032021</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>23.9868703446534</v>
       </c>
       <c r="E12" t="n">
-        <v>20.8979591836734</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>60</v>
+        <v>404.3</v>
       </c>
       <c r="I12" t="n">
-        <v>3410</v>
+        <v>263.5</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>383.3</v>
       </c>
       <c r="K12" t="n">
-        <v>77</v>
+        <v>1051.1</v>
       </c>
       <c r="L12" t="n">
-        <v>62</v>
+        <v>36.6</v>
       </c>
       <c r="M12" t="n">
-        <v>33</v>
+        <v>6.3</v>
       </c>
       <c r="N12" t="n">
-        <v>172</v>
+        <v>13.7</v>
       </c>
       <c r="O12" t="n">
-        <v>9</v>
+        <v>56.59999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>27.95</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="W12" t="n">
-        <v>2</v>
+        <v>27.7565571683219</v>
       </c>
       <c r="X12" t="n">
-        <v>22.25</v>
+        <v>27.2874765576698</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.145833333333333</v>
+        <v>1</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.2816399286988</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>22.1655797488585</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>270</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="AK12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2607</v>
+        <v>1228</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1988,43 +1884,43 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>81.77774745227769</v>
+        <v>85.5069068623723</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>32.4556777151202</v>
       </c>
       <c r="E13" t="n">
-        <v>28.1969212010364</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>56</v>
+        <v>39.8</v>
       </c>
       <c r="I13" t="n">
-        <v>536</v>
+        <v>30.3</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>26.9</v>
       </c>
       <c r="K13" t="n">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="L13" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -2033,34 +1929,34 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>21.55</v>
       </c>
       <c r="V13" t="n">
-        <v>8</v>
+        <v>0.34</v>
       </c>
       <c r="W13" t="n">
-        <v>2</v>
+        <v>22.5362872421696</v>
       </c>
       <c r="X13" t="n">
-        <v>23.5</v>
+        <v>21.3554558707986</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.272058823529412</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>23.5867074102368</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>22.8860247016979</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -2081,30 +1977,21 @@
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>82</v>
-      </c>
-      <c r="AN13" t="n">
         <v>210</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1736</v>
+        <v>2169</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2112,91 +1999,91 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>86.46788494689081</v>
+        <v>79.1083821646767</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>23.1836734693877</v>
       </c>
       <c r="E14" t="n">
-        <v>24.8579545454545</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>60</v>
+        <v>696.4</v>
       </c>
       <c r="I14" t="n">
-        <v>4130</v>
+        <v>556.8</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>561.3</v>
       </c>
       <c r="K14" t="n">
-        <v>187.8</v>
+        <v>1814.5</v>
       </c>
       <c r="L14" t="n">
-        <v>186.2</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>239</v>
+        <v>44.3</v>
       </c>
       <c r="N14" t="n">
-        <v>613</v>
+        <v>52.8</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>25.25</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="W14" t="n">
-        <v>1</v>
+        <v>25.6557168321874</v>
       </c>
       <c r="X14" t="n">
-        <v>27.2</v>
+        <v>24.2129335077053</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.192691029900332</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>27.3745861981156</v>
+        <v>1</v>
       </c>
       <c r="AA14" t="n">
-        <v>26.9117274486368</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2211,22 +2098,13 @@
         <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN14" t="inlineStr"/>
+        <v>96</v>
+      </c>
+      <c r="AK14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>501</v>
+        <v>365</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2234,40 +2112,40 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>80.7024477463432</v>
+        <v>86.5307742033615</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>30.4878048780487</v>
       </c>
       <c r="E15" t="n">
-        <v>24.7675659198292</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>60</v>
+        <v>145</v>
       </c>
       <c r="I15" t="n">
-        <v>983</v>
+        <v>62</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="K15" t="n">
-        <v>37</v>
+        <v>274</v>
       </c>
       <c r="L15" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2285,34 +2163,34 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>22.25</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="n">
-        <v>2</v>
+        <v>22.2816399286988</v>
       </c>
       <c r="X15" t="n">
-        <v>19.8</v>
+        <v>21.4950646217447</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.191780821917808</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.0534759358289</v>
+        <v>1</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.9279552640389</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2321,36 +2199,25 @@
         <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>132</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="AK15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2319</v>
+        <v>1429</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2358,46 +2225,46 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>77.2493207024615</v>
+        <v>89.07960906406061</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>36.71875</v>
       </c>
       <c r="E16" t="n">
-        <v>28.515625</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>60</v>
+        <v>522.4</v>
       </c>
       <c r="I16" t="n">
-        <v>348</v>
+        <v>255.8</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>169.8</v>
       </c>
       <c r="K16" t="n">
-        <v>55.8</v>
+        <v>948</v>
       </c>
       <c r="L16" t="n">
-        <v>46.7</v>
+        <v>89.5</v>
       </c>
       <c r="M16" t="n">
-        <v>14.9</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>117.4</v>
+        <v>28.3</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>117.8</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2406,31 +2273,31 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>23.45</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="W16" t="n">
-        <v>2</v>
+        <v>23.7458619811561</v>
       </c>
       <c r="X16" t="n">
-        <v>22.8</v>
+        <v>23.6114412754479</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.197628458498024</v>
+        <v>1</v>
       </c>
       <c r="Z16" t="n">
-        <v>22.5362872421696</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>22.1741916431478</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -2439,7 +2306,7 @@
         <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2451,30 +2318,21 @@
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>86</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>190</v>
+        <v>230</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>715</v>
+        <v>533</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2482,79 +2340,79 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>82.9500172383198</v>
+        <v>71.4425887900221</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>25.2595155709342</v>
       </c>
       <c r="E17" t="n">
-        <v>24.9134948096885</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>416</v>
       </c>
       <c r="I17" t="n">
-        <v>432</v>
+        <v>366</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>267</v>
       </c>
       <c r="K17" t="n">
-        <v>381</v>
+        <v>1049</v>
       </c>
       <c r="L17" t="n">
-        <v>226</v>
+        <v>40</v>
       </c>
       <c r="M17" t="n">
-        <v>240</v>
+        <v>25</v>
       </c>
       <c r="N17" t="n">
-        <v>847</v>
+        <v>35</v>
       </c>
       <c r="O17" t="n">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>39</v>
+        <v>24.35</v>
       </c>
       <c r="V17" t="n">
-        <v>106</v>
+        <v>0.18</v>
       </c>
       <c r="W17" t="n">
-        <v>1</v>
+        <v>24.5098039215686</v>
       </c>
       <c r="X17" t="n">
-        <v>20.2</v>
+        <v>24.1181250506758</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.220264317180617</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="n">
-        <v>21.3267125031831</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.7478091382848</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2563,42 +2421,33 @@
         <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="AK17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>74</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>168</v>
+        <v>178</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2746</v>
+        <v>685</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2606,77 +2455,79 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>84.10215399776919</v>
+        <v>86.0683245874211</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>21.484375</v>
       </c>
       <c r="E18" t="n">
-        <v>21.4902855137932</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>60</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
+        <v>153</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>65</v>
+        <v>153</v>
       </c>
       <c r="L18" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="M18" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>13</v>
+        <v>19.8</v>
       </c>
       <c r="V18" t="n">
-        <v>13</v>
+        <v>0.26</v>
       </c>
       <c r="W18" t="n">
-        <v>2</v>
+        <v>20.690094219506</v>
       </c>
       <c r="X18" t="n">
-        <v>22.75</v>
+        <v>20.1186577456453</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.302238805970149</v>
+        <v>1</v>
       </c>
       <c r="Z18" t="n">
-        <v>22.7272727272727</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>22.0994437339948</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -2697,28 +2548,21 @@
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>91</v>
-      </c>
-      <c r="AN18" t="inlineStr"/>
+        <v>182</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2169</v>
+        <v>1849</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2726,86 +2570,88 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>79.1083821646767</v>
+        <v>79.69184339113239</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>25.9259259259259</v>
       </c>
       <c r="E19" t="n">
-        <v>23.1836734693877</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>60</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
+        <v>417</v>
+      </c>
+      <c r="I19" t="n">
+        <v>426</v>
+      </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>202</v>
       </c>
       <c r="K19" t="n">
-        <v>696.4</v>
+        <v>1045</v>
       </c>
       <c r="L19" t="n">
-        <v>556.8</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>561.3</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1814.5</v>
+        <v>8</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P19" t="n">
-        <v>44.3</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>52.8</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>97.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>26.35</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>26.1013496307614</v>
       </c>
       <c r="X19" t="n">
-        <v>25.25</v>
+        <v>25.8994624442976</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.282312925170068</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>25.6557168321874</v>
+        <v>1</v>
       </c>
       <c r="AA19" t="n">
-        <v>24.2129335077053</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2823,22 +2669,13 @@
         <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>96</v>
-      </c>
-      <c r="AN19" t="inlineStr"/>
+        <v>124</v>
+      </c>
+      <c r="AK19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>466</v>
+        <v>2178</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2846,94 +2683,94 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>71.8237397964357</v>
+        <v>79.7736672624027</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>30.0432622977087</v>
       </c>
       <c r="E20" t="n">
-        <v>43.3862813295564</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>60</v>
+        <v>545.4</v>
       </c>
       <c r="I20" t="n">
-        <v>920</v>
+        <v>113.2</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>43.6</v>
       </c>
       <c r="K20" t="n">
-        <v>432</v>
+        <v>702.2</v>
       </c>
       <c r="L20" t="n">
-        <v>414</v>
+        <v>62.3</v>
       </c>
       <c r="M20" t="n">
-        <v>102</v>
+        <v>7.3</v>
       </c>
       <c r="N20" t="n">
-        <v>948</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>6</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>19</v>
+        <v>16.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>16.8</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>25.1</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="W20" t="n">
-        <v>2</v>
+        <v>25.3374076903489</v>
       </c>
       <c r="X20" t="n">
-        <v>21.45</v>
+        <v>24.9966585942398</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.32421875</v>
+        <v>1</v>
       </c>
       <c r="Z20" t="n">
-        <v>21.3267125031831</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>20.6494194474218</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -2945,24 +2782,13 @@
         <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>166</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="AK20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>529</v>
+        <v>692</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2970,82 +2796,82 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>79.79619552817709</v>
+        <v>83.7517216138109</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>31.6262764822435</v>
       </c>
       <c r="E21" t="n">
-        <v>27.7176852352623</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>60</v>
+        <v>554.9</v>
       </c>
       <c r="I21" t="n">
-        <v>724</v>
+        <v>349.2</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>311.7</v>
       </c>
       <c r="K21" t="n">
-        <v>360</v>
+        <v>1215.8</v>
       </c>
       <c r="L21" t="n">
-        <v>505</v>
+        <v>20.7</v>
       </c>
       <c r="M21" t="n">
-        <v>638</v>
+        <v>51.2</v>
       </c>
       <c r="N21" t="n">
-        <v>1503</v>
+        <v>74.2</v>
       </c>
       <c r="O21" t="n">
-        <v>39</v>
+        <v>146.1</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>78</v>
+        <v>10.3</v>
       </c>
       <c r="R21" t="n">
-        <v>117</v>
+        <v>8.4</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>18.7</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>10</v>
+        <v>23.75</v>
       </c>
       <c r="V21" t="n">
-        <v>10</v>
+        <v>0.21</v>
       </c>
       <c r="W21" t="n">
-        <v>1</v>
+        <v>24.1278329513624</v>
       </c>
       <c r="X21" t="n">
-        <v>22.15</v>
+        <v>23.5520684865315</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.28957528957529</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>23.2365673542144</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>22.1942730679895</v>
+        <v>1</v>
       </c>
       <c r="AB21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3057,7 +2883,7 @@
         <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -3066,27 +2892,18 @@
         <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>124</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>206</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1672</v>
+        <v>562</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -3094,43 +2911,43 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>85.7315332281289</v>
+        <v>85.7368640200776</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>20.8979591836734</v>
       </c>
       <c r="E22" t="n">
-        <v>26.0789715335169</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="I22" t="n">
-        <v>761</v>
+        <v>62</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="K22" t="n">
-        <v>122</v>
+        <v>172</v>
       </c>
       <c r="L22" t="n">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="M22" t="n">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="N22" t="n">
-        <v>238</v>
+        <v>10</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -3145,28 +2962,28 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>22.25</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="W22" t="n">
-        <v>1</v>
+        <v>22.2816399286988</v>
       </c>
       <c r="X22" t="n">
-        <v>24.2</v>
+        <v>22.1655797488585</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.271428571428571</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>23.8731856378915</v>
+        <v>1</v>
       </c>
       <c r="AA22" t="n">
-        <v>23.3675988578761</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3187,30 +3004,21 @@
         <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1</v>
+        <v>110</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1003</v>
+        <v>963</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3218,85 +3026,85 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>74.4512648300251</v>
+        <v>84.677171267777</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>25.5102040816326</v>
       </c>
       <c r="E23" t="n">
-        <v>30.6689049586776</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>60</v>
+        <v>84.2</v>
       </c>
       <c r="I23" t="n">
-        <v>139</v>
+        <v>130.6</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>175.5</v>
       </c>
       <c r="K23" t="n">
-        <v>309</v>
+        <v>390.3</v>
       </c>
       <c r="L23" t="n">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>668</v>
+        <v>14.7</v>
       </c>
       <c r="O23" t="n">
-        <v>20</v>
+        <v>14.7</v>
       </c>
       <c r="P23" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>19</v>
+        <v>21.2</v>
       </c>
       <c r="V23" t="n">
-        <v>19</v>
+        <v>0.3</v>
       </c>
       <c r="W23" t="n">
-        <v>1</v>
+        <v>22.6954418130889</v>
       </c>
       <c r="X23" t="n">
-        <v>25.05</v>
+        <v>21.5128218033123</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.307432432432432</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>24.8281130634072</v>
+        <v>1</v>
       </c>
       <c r="AA23" t="n">
-        <v>24.1971578951015</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3311,30 +3119,21 @@
         <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1</v>
+        <v>94</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>300</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1345</v>
+        <v>598</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3342,79 +3141,79 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>77.4494138971278</v>
+        <v>80.29658529165719</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>17.0068027210884</v>
       </c>
       <c r="E24" t="n">
-        <v>24.3374797187669</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I24" t="n">
-        <v>5850</v>
+        <v>129</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="K24" t="n">
-        <v>40.4</v>
+        <v>238</v>
       </c>
       <c r="L24" t="n">
-        <v>36.5</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>7.6</v>
+        <v>43</v>
       </c>
       <c r="N24" t="n">
-        <v>84.5</v>
+        <v>46</v>
       </c>
       <c r="O24" t="n">
-        <v>4.7</v>
+        <v>89</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>5.8</v>
+        <v>69</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>19.8</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="W24" t="n">
-        <v>1</v>
+        <v>19.7351667939903</v>
       </c>
       <c r="X24" t="n">
-        <v>23.7</v>
+        <v>19.1461601132455</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.211320754716981</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>23.8413547237077</v>
+        <v>1</v>
       </c>
       <c r="AA24" t="n">
-        <v>23.506086798771</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3441,22 +3240,15 @@
         <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>164</v>
-      </c>
-      <c r="AN24" t="inlineStr"/>
+        <v>180</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2073</v>
+        <v>514</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3464,77 +3256,79 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>86.328758302279</v>
+        <v>86.1886265115218</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>26.813590449954</v>
       </c>
       <c r="E25" t="n">
-        <v>33.6326530612244</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>60</v>
-      </c>
-      <c r="I25" t="inlineStr"/>
+        <v>560</v>
+      </c>
+      <c r="I25" t="n">
+        <v>108</v>
+      </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>277</v>
       </c>
       <c r="K25" t="n">
-        <v>1095.3</v>
+        <v>945</v>
       </c>
       <c r="L25" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>673.8</v>
+        <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>2369.1</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P25" t="n">
-        <v>31.4</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>31.4</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>21.9</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W25" t="n">
-        <v>1</v>
+        <v>22.2816399286988</v>
       </c>
       <c r="X25" t="n">
-        <v>30.35</v>
+        <v>20.903660546599</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.149390243902439</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>29.9847211611918</v>
+        <v>1</v>
       </c>
       <c r="AA25" t="n">
-        <v>29.7211204525439</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -3561,24 +3355,15 @@
         <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="AK25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>108</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>242</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>364</v>
+        <v>2010</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3586,83 +3371,85 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>83.7306500177453</v>
+        <v>84.44497680431969</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>23.0111768573307</v>
       </c>
       <c r="E26" t="n">
-        <v>27.639801313892</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>60</v>
-      </c>
-      <c r="I26" t="inlineStr"/>
+        <v>30.6</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>11.1</v>
       </c>
       <c r="K26" t="n">
-        <v>186</v>
+        <v>41.7</v>
       </c>
       <c r="L26" t="n">
-        <v>72</v>
+        <v>24.5</v>
       </c>
       <c r="M26" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>289</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>116</v>
+        <v>24.5</v>
       </c>
       <c r="P26" t="n">
-        <v>16</v>
+        <v>45.5</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>22</v>
+        <v>45.5</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>19.35</v>
       </c>
       <c r="V26" t="n">
-        <v>22</v>
+        <v>0.21</v>
       </c>
       <c r="W26" t="n">
-        <v>2</v>
+        <v>19.4805194805195</v>
       </c>
       <c r="X26" t="n">
-        <v>21.15</v>
+        <v>19.1826891138042</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.301204819277108</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>21.3267125031831</v>
+        <v>1</v>
       </c>
       <c r="AA26" t="n">
-        <v>20.8029488434442</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -3671,7 +3458,7 @@
         <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -3683,22 +3470,15 @@
         <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AK26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>84</v>
-      </c>
-      <c r="AN26" t="inlineStr"/>
+        <v>178</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>706</v>
+        <v>1227</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -3706,82 +3486,82 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>78.3421933226861</v>
+        <v>86.8977646905975</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>23.3843537414965</v>
       </c>
       <c r="E27" t="n">
-        <v>23.3066800530675</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>60</v>
+        <v>646</v>
       </c>
       <c r="I27" t="n">
-        <v>989</v>
+        <v>212</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>115</v>
       </c>
       <c r="K27" t="n">
-        <v>287.2</v>
+        <v>973</v>
       </c>
       <c r="L27" t="n">
-        <v>232.1</v>
+        <v>78</v>
       </c>
       <c r="M27" t="n">
-        <v>196.2</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>715.5</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>15.7</v>
+        <v>78</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>38.2</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>53.9</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>8</v>
+        <v>23.2</v>
       </c>
       <c r="V27" t="n">
-        <v>8</v>
+        <v>0.32</v>
       </c>
       <c r="W27" t="n">
-        <v>1</v>
+        <v>22.9182582123759</v>
       </c>
       <c r="X27" t="n">
-        <v>20.95</v>
+        <v>22.1655797488585</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.209401709401709</v>
+        <v>1</v>
       </c>
       <c r="Z27" t="n">
-        <v>21.5813598166539</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>21.1999238701354</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3805,19 +3585,10 @@
         <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>92</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>162</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
